--- a/resources/import/profile_payment_details.xlsx
+++ b/resources/import/profile_payment_details.xlsx
@@ -1,69 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Policy#</t>
-  </si>
-  <si>
-    <t>Issued Date</t>
-  </si>
-  <si>
-    <t>Policy</t>
-  </si>
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Sales Out</t>
-  </si>
-  <si>
-    <t>Insured Value</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13.0"/>
+      <name val="Arial"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -93,26 +65,89 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -310,79 +345,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.25"/>
-    <col customWidth="1" min="2" max="2" width="20.75"/>
-    <col customWidth="1" min="3" max="3" width="37.5"/>
-    <col customWidth="1" min="4" max="4" width="35.13"/>
-    <col customWidth="1" min="5" max="5" width="19.88"/>
-    <col customWidth="1" min="6" max="6" width="12.38"/>
-    <col customWidth="1" min="7" max="7" width="18.25"/>
-    <col customWidth="1" min="8" max="8" width="30.88"/>
+    <col width="27.25" customWidth="1" style="3" min="1" max="1"/>
+    <col width="20.75" customWidth="1" style="3" min="2" max="2"/>
+    <col width="37.5" customWidth="1" style="3" min="3" max="3"/>
+    <col width="35.13" customWidth="1" style="3" min="4" max="4"/>
+    <col width="19.88" customWidth="1" style="3" min="5" max="5"/>
+    <col width="12.38" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="22" customWidth="1" style="3" min="8" max="8"/>
+    <col width="22" customWidth="1" style="3" min="9" max="9"/>
+    <col width="22" customWidth="1" style="3" min="10" max="10"/>
+    <col width="22" customWidth="1" style="3" min="11" max="11"/>
+    <col width="22" customWidth="1" style="3" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Policy#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Insured Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Net Premium</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Gross Premium</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Client Payment Date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Policy Start Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Comm. Discount</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Accumulated Amount</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resources/import/profile_payment_details.xlsx
+++ b/resources/import/profile_payment_details.xlsx
@@ -350,82 +350,106 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="27.25" customWidth="1" style="3" min="1" max="1"/>
-    <col width="20.75" customWidth="1" style="3" min="2" max="2"/>
-    <col width="37.5" customWidth="1" style="3" min="3" max="3"/>
-    <col width="35.13" customWidth="1" style="3" min="4" max="4"/>
-    <col width="19.88" customWidth="1" style="3" min="5" max="5"/>
-    <col width="12.38" customWidth="1" style="3" min="6" max="6"/>
-    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="27.25" customWidth="1" style="3" min="2" max="2"/>
+    <col width="20.75" customWidth="1" style="3" min="3" max="3"/>
+    <col width="37.5" customWidth="1" style="3" min="4" max="4"/>
+    <col width="35.13" customWidth="1" style="3" min="5" max="5"/>
+    <col width="19.88" customWidth="1" style="3" min="6" max="6"/>
+    <col width="12.38" customWidth="1" style="3" min="7" max="7"/>
     <col width="22" customWidth="1" style="3" min="8" max="8"/>
     <col width="22" customWidth="1" style="3" min="9" max="9"/>
     <col width="22" customWidth="1" style="3" min="10" max="10"/>
     <col width="22" customWidth="1" style="3" min="11" max="11"/>
     <col width="22" customWidth="1" style="3" min="12" max="12"/>
+    <col width="16" customWidth="1" style="3" min="13" max="13"/>
+    <col width="22" customWidth="1" style="3" min="14" max="14"/>
+    <col width="18" customWidth="1" style="3" min="15" max="15"/>
+    <col width="16" customWidth="1" style="3" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>New/Renewal</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Policy#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Insured Value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Net Premium</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gross Premium</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Client Payment Date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Policy Start Date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Comm. Discount</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Sales out Comm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accumulated Amount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Car Brand</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Commission</t>
         </is>
       </c>
     </row>
@@ -442,6 +466,10 @@
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -456,6 +484,10 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -470,6 +502,10 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/import/profile_payment_details.xlsx
+++ b/resources/import/profile_payment_details.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
@@ -366,8 +366,8 @@
     <col width="22" customWidth="1" style="3" min="11" max="11"/>
     <col width="22" customWidth="1" style="3" min="12" max="12"/>
     <col width="16" customWidth="1" style="3" min="13" max="13"/>
-    <col width="22" customWidth="1" style="3" min="14" max="14"/>
-    <col width="18" customWidth="1" style="3" min="15" max="15"/>
+    <col width="18" customWidth="1" style="3" min="14" max="14"/>
+    <col width="16" customWidth="1" style="3" min="15" max="15"/>
     <col width="16" customWidth="1" style="3" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -439,15 +439,10 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Accumulated Amount</t>
+          <t>Car Brand</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Car Brand</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
@@ -469,7 +464,6 @@
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -487,7 +481,6 @@
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -505,7 +498,6 @@
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
